--- a/daily_matches/job_matches_2026-03-07.xlsx
+++ b/daily_matches/job_matches_2026-03-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Applied Artificial Intelligence Engineer</t>
+          <t>Software Engineer - AI Engineer II/III</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Vanderbilt University</t>
+          <t>Applied Medical</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Rancho Santa Margarita, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,7 +486,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Pinecone, Prompt Engineering, TensorFlow, PyTorch, Data Lake, MLflow, FastAPI, CI/CD</t>
+          <t>AI Engineer, LangChain, RAG, FAISS, Pinecone, ChromaDB, Prompt Engineering, TensorFlow, PyTorch, FastAPI</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,24 +496,24 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ca6504eac1ad121</t>
+          <t>https://www.indeed.com/viewjob?jk=921527a7644f024e</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Software Engineer - AI Engineer II/III</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>The Wyanoke Group</t>
+          <t>Applied Medical</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Thorofare, NJ, US USA</t>
+          <t>Rancho Santa Margarita, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, FAISS, Pinecone, Prompt Engineering, S3, Glue</t>
+          <t>AI Engineer, LangChain, RAG, FAISS, Pinecone, ChromaDB, Prompt Engineering, TensorFlow, PyTorch, FastAPI</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4c14d111aa82140</t>
+          <t>https://www.indeed.com/viewjob?jk=8e500f3ffb4971b2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Advisory Full Stack Engineer, AI Orchestration</t>
+          <t>Machine Learning Engineer 1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Lenovo</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>17.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, S3, Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka, PostgreSQL, MySQL</t>
+          <t>Machine Learning Engineer, TensorFlow, Jenkins, Git, Databricks, MySQL, MongoDB, Cassandra, Tableau, Matplotlib</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=438618d7e9a188f1</t>
+          <t>https://www.indeed.com/viewjob?jk=d9f4cd1d239989a5</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>GenAI Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bilt Rewards</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.6</v>
+        <v>17.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Terraform, BigQuery, Kafka, PostgreSQL, Tableau, Power BI, Python, SQL</t>
+          <t>AI Engineer, LangChain, RAG, Gemini, Prompt Engineering, TensorFlow, PyTorch, Keras, Git, NoSQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65fff7f62cd69416</t>
+          <t>https://www.indeed.com/viewjob?jk=b9f4cbf2f3b7823a</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>GenAI Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>GE Aerospace</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>17.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, S3, Glue, Redshift, Docker, Kubernetes, CI/CD, Terraform, Redshift, Python</t>
+          <t>AI Engineer, LangChain, RAG, Gemini, Prompt Engineering, TensorFlow, PyTorch, Keras, Git, NoSQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=029a23ee4433cc18</t>
+          <t>https://www.indeed.com/viewjob?jk=89fb8ea55ce169ab</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior AI Engineer (Cloud Architecture Concentration)</t>
+          <t>GenAI Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Risepoint</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.3</v>
+        <v>17.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, Kinesis, Docker, Kubernetes, AKS, CI/CD, Databricks, Kafka, Python, R</t>
+          <t>AI Engineer, LangChain, RAG, Gemini, Prompt Engineering, TensorFlow, PyTorch, Keras, Git, NoSQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa1ca36ea79ca418</t>
+          <t>https://www.indeed.com/viewjob?jk=6fda2fa21a921e27</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Software Delivery</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Box</t>
+          <t>Paychex, Inc.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>Data Scientist, RAG, Data Lake, CI/CD, Git, Snowflake, Databricks, PySpark, Python, SQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02b40c81b7ab0657</t>
+          <t>https://www.indeed.com/viewjob?jk=7e69293272ecf929</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Machine Learning / Software Engineer</t>
+          <t>Senior DevOps Software Engineer, Firmware &amp; CI/CD</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Vector Resources, Inc.</t>
+          <t>Rivian and Volkswagen Group Technologies</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Git, Kafka, Python, SQL</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91496c96bd53f770</t>
+          <t>https://www.indeed.com/viewjob?jk=3f1de60ecf2851e5</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Junior Dev Ops Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BlueVoyant</t>
+          <t>Concord Music Group, Inc.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, Python, SQL, R</t>
+          <t>Athena, Docker, Apache Airflow, Git, PostgreSQL, Python, SQL, R, Java, Julia</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,67 +776,67 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c61d3171a69dbbf1</t>
+          <t>https://www.indeed.com/viewjob?jk=a02820021c063a20</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AI Engineer III</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Premera Blue Cross</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Mountlake Terrace, WA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, Azure ML, Matplotlib, Python, R</t>
+          <t>RAG, Copilot, Docker, Kubernetes, AKS, Git, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d53c8cc2f397f05d</t>
+          <t>https://www.indeed.com/viewjob?jk=157b50a41060d271</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AI &amp; Machine Learning Engineer</t>
+          <t>Intern- AI/ML Engineering</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>OneBlood</t>
+          <t>ENERCON SERVICES, INC</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Kennesaw, GA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Keras, CI/CD, Git, Python, SQL, R</t>
+          <t>AI Engineer, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Azure ML, Python, R, Optimization</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=481be343fdc2f8fc</t>
+          <t>https://www.indeed.com/viewjob?jk=dd0b2d0b4cbd0c81</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Back-End Java Engineer</t>
+          <t>Senior Frontend Engineer (Angular) – Healthcare SaaS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>BRMi</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Davie, FL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Docker, CI/CD, Jenkins, Git, Power BI, SQL, R, Java, Scala</t>
+          <t>Generative AI, RAG, Copilot, S3, CI/CD, Git, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbe04a589c275aec</t>
+          <t>https://www.indeed.com/viewjob?jk=5562384a8af5c1c8</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Automation &amp; Digitalization Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Royal Credit Union</t>
+          <t>Siemens Energy</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Gibsonton, FL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Redshift, Kubernetes, Git, Snowflake, Databricks, Redshift, Python, SQL, R</t>
+          <t>Generative AI, RAG, CI/CD, Git, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac872219b95c53aa</t>
+          <t>https://www.indeed.com/viewjob?jk=ab0f9eeafd2e5948</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Analyst</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Royal Credit Union</t>
+          <t>Young Living Essential Oils</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Eau Claire, WI, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Redshift, Kubernetes, Git, Snowflake, Databricks, Redshift, Python, SQL, R</t>
+          <t>RAG, Cortex, Snowflake, Tableau, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,102 +951,102 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbbea7e961352216</t>
+          <t>https://www.indeed.com/viewjob?jk=f6e7033c4d1b95dc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Scientist, GenAI</t>
+          <t>AI Agent ML Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>AIG</t>
+          <t>Bausch &amp; Lomb</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, LLaMA, Prompt Engineering, PyTorch, Git, Python, R, Scala</t>
+          <t>LangChain, Pinecone, Prompt Engineering, TensorFlow, PyTorch, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d176815431eaffa</t>
+          <t>https://www.indeed.com/viewjob?jk=a668ac65825b4ffb</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer (Hybrid)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>American Medical Association (AMA)</t>
+          <t>INTRAFI</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Data Lake, CI/CD, Terraform, Databricks, Python, SQL, R, Scala</t>
+          <t>Generative AI, RAG, Copilot, CI/CD, Jenkins, Git, SQL, R, Java</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58b8869ff6d42582</t>
+          <t>https://www.indeed.com/viewjob?jk=58dc0e1f32b53bda</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Engineer II (Full Stack Java/React) - Commissions Platform - HYBRID</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Prompt Engineering, CI/CD, Git, NoSQL, SQL, R, Java, Scala</t>
+          <t>Apache Airflow, GitHub Actions, Git, Kafka, NoSQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab92260f020b4cb4</t>
+          <t>https://www.indeed.com/viewjob?jk=4aa67c824506bfe6</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Engineer II (Full Stack Java/React) - Commissions Platform - HYBRID</t>
+          <t>Engineer, Development Tax Technology | Denver Summer/Fall 2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Prompt Engineering, CI/CD, Git, NoSQL, SQL, R, Java, Scala</t>
+          <t>RAG, AKS, Git, Databricks, Tableau, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,252 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=487ef0decd6add43</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Senior Full Stack Engineer (Application Stack)</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Quanta Credit Services</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>EC2, CI/CD, Terraform, Git, Snowflake, Kafka, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=eb2933f331e6e0d8</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Forward Deployed Full-Stack Engineer (Mid-level)</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Groton, CT, US USA</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, PostgreSQL, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4e51f03984b620ba</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Forward Deployed Full-Stack Engineer (Senior)</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Groton, CT, US USA</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, PostgreSQL, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=43717ca0bf8a0bb1</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Senior Engineer - Digital Products</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Brooks Running</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>10</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>RAG, CI/CD, GitHub Actions, Git, Python, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f16fd945a232682b</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Customer Centric Engineer</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Workato</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>10</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>RAG, Kafka, PostgreSQL, NoSQL, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=80d0f3075e8e2d2c</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Full Stack Node/Typescript Engineer</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Culmen International, LLC</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>RAG, Gemini, BigQuery, Git, BigQuery, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=37b3576be0dd88d6</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>.NET Developer – Azure DevOps Specialist</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Fyin.com</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Denver, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>10</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Docker, AKS, CI/CD, Terraform, Git, R, Scala</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=75f30913de1b7459</t>
+          <t>https://www.indeed.com/viewjob?jk=767abd17312c8d91</t>
         </is>
       </c>
     </row>
